--- a/output/pdf_financials_xlsx/KEON.H.xlsx
+++ b/output/pdf_financials_xlsx/KEON.H.xlsx
@@ -4758,28 +4758,28 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.171548</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.221548</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.221548</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.42745</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.951526</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.327481</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.358806</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.358806</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>2.358806</v>
@@ -10015,7 +10015,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -11093,7 +11097,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="n">
         <v>1.171548</v>
       </c>
@@ -11444,7 +11452,11 @@
           <t>Share-based payment reserve 12</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KEON.H.xlsx
+++ b/output/pdf_financials_xlsx/KEON.H.xlsx
@@ -909,19 +909,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000188</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000112</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>4.5e-05</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.00436</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1651,19 +1651,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.899491</v>
+        <v>-1.899679</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.268418</v>
+        <v>-0.26853</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.442411</v>
+        <v>-0.442456</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.991032</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.112178</v>
+        <v>-1.116538</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-2.095854</v>
@@ -1743,19 +1743,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.899491</v>
+        <v>-1.899679</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.268418</v>
+        <v>-0.26853</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.442411</v>
+        <v>-0.442456</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.991032</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.112178</v>
+        <v>-1.116538</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-2.095854</v>
@@ -1986,40 +1986,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.286509</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.091194</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.307098</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.562718</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.887917</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.474363</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.067592</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.010318</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.001189</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.156624</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.004459</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000612</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0</v>
@@ -2078,40 +2078,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.286509</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.091194</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.307098</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.562718</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.887917</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.030404</v>
+        <v>0.504767</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.025977</v>
+        <v>0.093569</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.010318</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.001189</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.156624</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.004459</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.000612</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>0</v>
@@ -2630,40 +2630,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.292487</v>
+        <v>0.005978</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.101177</v>
+        <v>0.009983000000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.30859</v>
+        <v>0.001492</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.581273</v>
+        <v>0.018555</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.915455</v>
+        <v>0.027538</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.530372</v>
+        <v>0.056009</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.067592</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.001189</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.187874</v>
+        <v>0.03125</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.007202</v>
+        <v>0.002743</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.000612</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0</v>
@@ -6977,7 +6977,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
@@ -27370,7 +27370,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -28069,7 +28069,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -28640,7 +28640,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -31663,7 +31663,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E314" s="5" t="n">

--- a/output/pdf_financials_xlsx/KEON.H.xlsx
+++ b/output/pdf_financials_xlsx/KEON.H.xlsx
@@ -6072,7 +6072,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>2.129882</v>
       </c>
       <c r="H120" s="3" t="n">
         <v>0</v>
@@ -15398,7 +15398,11 @@
           <t>Proceeds on issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KEON.H.xlsx
+++ b/output/pdf_financials_xlsx/KEON.H.xlsx
@@ -679,28 +679,28 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.138937</v>
+        <v>0.186937</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.099347</v>
+        <v>0.147347</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.060874</v>
+        <v>0.108874</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.129038</v>
+        <v>0.182038</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.335907</v>
+        <v>0.453907</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.282176</v>
+        <v>0.420176</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.150962</v>
+        <v>0.210962</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.09589399999999999</v>
+        <v>0.09641</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>0.032765</v>
@@ -5623,10 +5623,10 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001191</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004724</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -5827,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.01648</v>
       </c>
       <c r="I115" s="1" t="inlineStr">
         <is>
@@ -6761,10 +6761,10 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001191</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004724</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -6809,10 +6809,10 @@
         <v>-0.226251</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.238228</v>
+        <v>-0.239419</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.438282</v>
+        <v>-0.443006</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-0.976854</v>
@@ -13218,7 +13218,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -14071,7 +14075,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -15955,7 +15963,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -29890,7 +29902,11 @@
           <t>Directors’ fees 8</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -30745,7 +30761,11 @@
           <t>Directors’ fees 12</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E302" s="5" t="n">
         <v>0.048</v>
       </c>
@@ -32295,7 +32315,11 @@
           <t>Directors’ fees 13</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
